--- a/public/pilateacher-migration-template.xlsx
+++ b/public/pilateacher-migration-template.xlsx
@@ -109,70 +109,106 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">실패해도 나머지는 저장됩니다</t>
+          <t xml:space="preserve">단가는 넣지 않습니다</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 실패한 행만 고쳐서 다시 올리면 됩니다.</t>
+          <t xml:space="preserve">· 회당 단가는 급여카테고리가 정합니다. 손으로 적지 않습니다.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 같은 파일을 두 번 올려도 회원권이 두 번 발급되지 않습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20"/>
+          <t xml:space="preserve">· "1:1 재등록(정상)"은 담당 강사의 풀방금액으로 계산합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  앱의 [강사 단가]에서 그 강사의 풀방금액을 먼저 넣어 주세요.</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">강사누적진행</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">· 그 강사가 그 회원에게 지금까지 진행한 횟수입니다.</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">· "기타"는 정해진 단가가 없어 올릴 수 없습니다. 앱에서 직접 발급해 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 급여 단가가 이 숫자로 갈리므로 가능한 한 정확히 넣어 주세요.</t>
+          <t xml:space="preserve">실패해도 나머지는 저장됩니다</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 모르는 건은 99 를 넣으면 기준 단가부터 시작합니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">남은횟수 · 계약일 · 만료일</t>
-        </is>
-      </c>
-    </row>
+          <t xml:space="preserve">· 실패한 행만 고쳐서 다시 올리면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 같은 파일을 두 번 올려도 회원권이 두 번 발급되지 않습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">· 남은횟수는 9월 말일 기준으로 남은 회차입니다.</t>
+          <t xml:space="preserve">강사누적진행</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 그 강사가 그 회원에게 지금까지 진행한 횟수입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 급여 단가가 이 숫자로 갈리므로 가능한 한 정확히 넣어 주세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 모르는 건은 99 를 넣으면 기준 단가부터 시작합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">남은횟수 · 계약일 · 만료일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">· 남은횟수는 9월 말일 기준으로 남은 회차입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
         <is>
           <t xml:space="preserve">· 날짜는 2026-09-30 또는 2026/9/30 형식으로 넣어 주세요.</t>
         </is>
